--- a/MCMC-ABC_results/scan_prior_st.xlsx
+++ b/MCMC-ABC_results/scan_prior_st.xlsx
@@ -474,11 +474,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -601,34 +601,34 @@
         <v>0.1</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.55</v>
+        <v>0.4222</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-0.03411</v>
+        <v>-0.11448</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.11494</v>
+        <v>0.33959</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.07617</v>
+        <v>0.06877999999999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.14346</v>
+        <v>0.0635</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.29553</v>
+        <v>0.25869</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.53184</v>
+        <v>0.24135</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.21578</v>
+        <v>0.06958</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.06617000000000001</v>
+        <v>0.03627</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.02463</v>
+        <v>0.02903</v>
       </c>
     </row>
     <row r="6">
@@ -636,244 +636,3429 @@
         <v>0.1</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3</v>
+        <v>0.7444</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01288</v>
+        <v>-0.07646</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0353</v>
+        <v>0.25884</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.07761</v>
+        <v>0.07288</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.17082</v>
+        <v>0.09544999999999999</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.29815</v>
+        <v>0.28072</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.59789</v>
+        <v>0.35902</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.26305</v>
+        <v>0.13209</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.0617</v>
+        <v>0.05814</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01015</v>
+        <v>0.03585</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>1.55</v>
+        <v>0.1</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.1</v>
+        <v>1.0667</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.25757</v>
+        <v>-0.05148</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.4631</v>
+        <v>0.19105</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.02453</v>
+        <v>0.07645</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.008630000000000001</v>
+        <v>0.11868</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.09375</v>
+        <v>0.3002</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.03179</v>
+        <v>0.45252</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.00325</v>
+        <v>0.17477</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.00332</v>
+        <v>0.07227</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.00289</v>
+        <v>0.03336</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>1.55</v>
+        <v>0.1</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1.55</v>
+        <v>1.3889</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.09327000000000001</v>
+        <v>-0.03582</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.17906</v>
+        <v>0.14288</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1065</v>
+        <v>0.07697</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.16143</v>
+        <v>0.13313</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.39013</v>
+        <v>0.29697</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.58111</v>
+        <v>0.50947</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.24434</v>
+        <v>0.20271</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03853</v>
+        <v>0.06073</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01913</v>
+        <v>0.02512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>1.55</v>
+        <v>0.1</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3</v>
+        <v>1.7111</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.03093</v>
+        <v>-0.02842</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-0.02583</v>
+        <v>0.08265</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.1067</v>
+        <v>0.0779</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.19208</v>
+        <v>0.14986</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.39797</v>
+        <v>0.29962</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.65203</v>
+        <v>0.54334</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.30194</v>
+        <v>0.22748</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.03245</v>
+        <v>0.06965</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.01082</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.1</v>
+        <v>2.0333</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.25305</v>
+        <v>-0.02331</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.46272</v>
+        <v>0.05356</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.02263</v>
+        <v>0.07704</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.00791</v>
+        <v>0.1555</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.09353</v>
+        <v>0.29668</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.03424</v>
+        <v>0.56916</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.00281</v>
+        <v>0.23657</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.00342</v>
+        <v>0.05797</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.00336</v>
+        <v>0.01621</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.55</v>
+        <v>2.3556</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-0.08867999999999999</v>
+        <v>-0.01721</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1587</v>
+        <v>0.00337</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.1064</v>
+        <v>0.0788</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1595</v>
+        <v>0.16401</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.39253</v>
+        <v>0.30206</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.57089</v>
+        <v>0.5877</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.24653</v>
+        <v>0.25263</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.04151</v>
+        <v>0.0546</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.01986</v>
+        <v>0.01204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-0.01351</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-0.02082</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.07785</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.16862</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.5928099999999999</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.06216</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.01022</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="C13" s="5" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.07725</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.16856</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.5939</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.05692</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.00978</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-0.25142</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.46466</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.02015</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.04091</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.00272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.20231</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.07376000000000001</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.06265</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.2266</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.07228999999999999</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.02546</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.02085</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-0.1544</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.09276</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.10475</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.14792</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0.04872</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.02995</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.11788</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.12987</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.20192</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.03206</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-0.09145</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.10363</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.14548</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.5325</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.05901</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.03156</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-0.07630000000000001</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.14012</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.10509</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.16193</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.58036</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.25336</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.0231</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.10238</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.17538</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.62202</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.0169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.04604</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.10514</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.18076</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.64493</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.0133</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.01933</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.10459</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.18858</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.66717</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0.03168</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.01155</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>-0.03506</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-0.00616</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.10794</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.19445</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0.40217</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0.67491</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0.30026</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.0282</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0.01009</v>
+      <c r="C23" s="5" t="n">
+        <v>-0.03665</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.10658</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.19157</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.65935</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.02418</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-0.25643</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.46065</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.02537</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.10161</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.00298</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-0.20743</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.07059</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.06039</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.22258</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.07188</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0.02772</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.02395</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-0.15829</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.09077</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.09872</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.15017</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.04911</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.03618</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.09858</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.12989</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0.19848</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.02515</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-0.10034</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.19031</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0.10533</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.15276</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.56327</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.02189</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-0.0771</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.13819</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.10883</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.17088</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.60316</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0.25396</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0.03507</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.01835</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-0.06651</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.11167</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.10845</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.62339</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.27194</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.02043</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>-0.05173</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.10981</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.18558</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.64843</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0.03161</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.01432</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0.11063</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.19514</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.66605</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0.02784</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.01138</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>-0.03674</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.10681</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.19313</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.66123</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0.02771</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.0108</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>-0.25079</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0.02398</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.09923</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.00358</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.00327</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>-0.21013</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.07038</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.06081</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.22411</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.06983</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0.02575</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.02156</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-0.15989</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0.09200999999999999</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.10003</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.14767</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.04442</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.03297</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>-0.13045</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0.25292</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.13108</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.19634</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.03135</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>-0.09952</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.19602</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.10511</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.15167</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.55304</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.02629</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>-0.07588</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0.14561</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.10691</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.16506</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.5986399999999999</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.25869</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.01879</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>-0.06333999999999999</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0.08918</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.17814</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.62664</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0.03563</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.01499</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>-0.05516</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.07517</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.10833</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.18478</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.65119</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.03277</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.01344</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.03898</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0.6571900000000001</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0.02724</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.0113</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>-0.03381</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.10756</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.19338</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.66681</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.01055</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>-0.25762</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.008109999999999999</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.10715</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0.02919</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.00306</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>-0.20935</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.06845</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.06221</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.25885</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.23427</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.07004000000000001</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.03171</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.02117</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>-0.15942</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.08971999999999999</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.10002</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0.14669</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.03496</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>-0.12385</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.13106</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.47844</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.19802</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.02473</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>-0.09944</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.19182</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.10412</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.14938</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.54112</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.22903</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0.05294</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.02765</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>-0.07511</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.13296</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.10764</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.16618</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.5959100000000001</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.04738</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.02045</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>-0.07194</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0.11487</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.10795</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.17789</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.62407</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.26834</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0.03943</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0.01682</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-0.05292</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.10784</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.18625</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.65793</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.01256</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.10824</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.19067</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0.66228</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>0.03082</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0.01312</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>-0.03851</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>-0.00221</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.10828</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.67118</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.03227</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.01369</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>-0.25867</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.02228</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.00835</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.07951</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.02959</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.00206</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.00274</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>-0.20926</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.06943000000000001</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.05652</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.25907</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.06821000000000001</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.02754</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.02112</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>-0.16214</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.09032</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.10322</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0.14125</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>0.04622</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0.02438</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>-0.1277</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0.25139</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.09999</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.12582</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.46255</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.19305</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.04878</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.02898</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>-0.09680999999999999</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>0.18774</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.10454</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.15074</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.54303</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>0.23563</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.02617</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>-0.08728</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0.15555</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.10697</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.16244</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.58541</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.24938</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.03683</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.0194</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>-0.06487</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>0.10185</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.10915</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0.6377699999999999</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0.01735</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>-0.05803</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0.07381</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.10814</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.18589</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.65467</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0.01448</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0.01654</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.10866</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.19159</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0.6629</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0.01337</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>-0.03869</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.10667</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.67032</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0.02727</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.00944</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>-0.25771</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0.46242</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0.009090000000000001</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0.09161</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>0.00292</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>-0.20756</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.07112</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.06157</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.06929</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>0.02918</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0.01895</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>-0.16009</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0.09243999999999999</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0.10166</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>0.14817</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>0.05023</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>0.03722</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>-0.12293</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0.23983</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.10044</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.13024</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.19777</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>0.05127</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0.03178</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>-0.09987</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>0.10546</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.15104</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>0.23121</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>0.04308</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>0.02438</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>-0.08702</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.10876</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.16772</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.60161</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>0.03815</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.01983</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>-0.07011000000000001</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0.11063</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0.64429</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0.26911</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0.02969</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>0.01484</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>-0.04746</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>0.04512</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.10841</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.18778</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.40209</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.66653</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0.02895</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0.01227</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>-0.04716</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0.03715</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0.19068</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0.66595</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>0.01374</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>-0.03338</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>-0.01523</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.10799</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.19165</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.6702</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>0.02989</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0.01203</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>-0.25424</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0.46209</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0.08198</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0.00292</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>0.00295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>-0.20191</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0.07121</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.05929</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.22661</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.07011000000000001</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>0.02009</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>-0.16188</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0.09159</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0.10035</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>0.04706</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>0.03388</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>-0.12597</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>0.24836</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0.10057</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.13026</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0.19798</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>0.04634</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0.03094</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>-0.09828000000000001</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0.18429</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0.15477</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0.55536</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>0.23098</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0.02272</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>-0.08081000000000001</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>0.14849</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.10434</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.16181</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0.5791500000000001</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.04698</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0.02311</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>-0.06099</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>0.08679000000000001</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0.10933</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0.18475</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>0.6408700000000001</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>0.03174</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>0.01417</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>-0.06486</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>0.08588</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.10974</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.18167</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0.63586</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>0.03306</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.01531</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>0.01759</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0.10755</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0.19426</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0.66547</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.01117</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>-0.03423</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>-0.02239</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.10891</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.19898</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.67337</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.02514</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.00954</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B84" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>-0.2533</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0.01933</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0.06924</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>0.03518</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>0.00208</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>0.00302</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>0.00285</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>-0.20474</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0.22147</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0.01613</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B86" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>-0.16044</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0.10373</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>0.04708</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>0.03043</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>-0.12601</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.12818</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.47489</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.19723</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0.02979</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B88" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>-0.10458</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>0.20042</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0.10556</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0.14919</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>0.04867</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>0.02767</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>-0.07915999999999999</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>0.13803</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.10636</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.16584</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.59143</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>0.25653</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0.04503</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.02008</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B90" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>-0.06176</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>0.10811</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>0.17854</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>0.63048</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>0.01804</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>-0.05478</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.11053</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.18806</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.65706</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.03046</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>0.01332</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B92" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>-0.03975</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>0.02778</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>0.10625</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0.18661</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>0.64923</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="K92" s="4" t="n">
+        <v>0.01402</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>-0.0316</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>-0.01046</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.19054</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.6646300000000001</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0.01111</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>-0.24687</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>0.46241</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>0.02596</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0.11111</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>0.00373</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>-0.21234</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0.06984</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0.05962</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.25464</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>0.22746</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.03149</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" s="4" t="n">
+        <v>0.7444</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>-0.15782</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>0.09036</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>0.05272</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>0.03837</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>1.0667</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>-0.12605</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.10094</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.13003</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.47936</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.20036</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0.03405</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" s="4" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>-0.10315</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>0.18852</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>0.10661</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0.15761</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0.57064</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>0.23292</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>0.02354</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>1.7111</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>-0.07974000000000001</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>0.14489</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.10811</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.16672</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.59966</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.25263</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0.04484</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.02275</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" s="4" t="n">
+        <v>2.0333</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>-0.06347</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0.09532</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0.10865</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="J100" s="4" t="n">
+        <v>0.04094</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>0.01911</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>2.3556</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>-0.05338</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>0.06408</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.10776</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.18693</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.64703</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0.01203</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="4" t="n">
+        <v>2.6778</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>0.10924</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0.19391</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>0.67354</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>0.02526</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>0.01053</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>-0.04049</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>-0.00315</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>0.10998</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.19037</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.6615799999999999</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>0.009849999999999999</v>
       </c>
     </row>
   </sheetData>
